--- a/public/templates/vendor_upload_template.xlsx
+++ b/public/templates/vendor_upload_template.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC984461-CBAB-4072-B74E-58B97B14402A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F039B800-EE24-4F3A-86A2-ADBC6810A419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor" sheetId="1" r:id="rId1"/>
-    <sheet name="data" sheetId="3" r:id="rId2"/>
+    <sheet name="data" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Email</t>
   </si>
@@ -54,15 +54,9 @@
     <t>Vendor Name</t>
   </si>
   <si>
-    <t>Deepthi Shetty</t>
-  </si>
-  <si>
     <t>ERP</t>
   </si>
   <si>
-    <t>dshetty@slideinsurance.com</t>
-  </si>
-  <si>
     <t>SlideWire</t>
   </si>
   <si>
@@ -102,125 +96,35 @@
     <t>ScrumMaster</t>
   </si>
   <si>
-    <t>eokafor@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Eric Okafor</t>
-  </si>
-  <si>
-    <t>lsherman@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Leonid Sherman</t>
-  </si>
-  <si>
-    <t>mnaeem@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Muhammad Bilal Naeem</t>
-  </si>
-  <si>
-    <t>nmittapally@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Naresh Mittapally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ngoud@slideinsurance.com  </t>
-  </si>
-  <si>
-    <t>Naveen Goud</t>
-  </si>
-  <si>
-    <t>Vilma Adamu</t>
-  </si>
-  <si>
-    <t>vadamu@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>vshah@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Vishwang Shah</t>
-  </si>
-  <si>
-    <t>Appala Raju Allaboina</t>
-  </si>
-  <si>
-    <t>Rajkumar Patel</t>
-  </si>
-  <si>
-    <t>Saikrishna Jindam</t>
-  </si>
-  <si>
-    <t>aallaboina@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>rapatel@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>sjindam@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Christine Prioleau</t>
-  </si>
-  <si>
-    <t>Hampton Brabham</t>
-  </si>
-  <si>
-    <t>Laurie Sisak</t>
-  </si>
-  <si>
-    <t>Liz Smith</t>
-  </si>
-  <si>
-    <t>Priyesh Keshare</t>
-  </si>
-  <si>
-    <t>Sanjeet Das</t>
-  </si>
-  <si>
-    <t>cprioleau@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>hbrabham@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>lsisak@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>lsmith@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>pkeshare@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>sadas@slideinsurance.com</t>
+    <t>LTM</t>
+  </si>
+  <si>
+    <t>Value Momemtum</t>
+  </si>
+  <si>
+    <t>JBK</t>
+  </si>
+  <si>
+    <t>EY</t>
+  </si>
+  <si>
+    <t>DuckCreek</t>
+  </si>
+  <si>
+    <t>NTT Data</t>
+  </si>
+  <si>
+    <t>Invenger</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -243,17 +147,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -586,12 +486,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5412F18-43F0-4B39-A3A8-2B1B8B345020}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -612,316 +513,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{5D3955B8-32B2-4299-81C8-4985A8C7E14C}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{BD965931-02AB-41C3-9375-7ECF8FAABDF6}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{ECDDC6AB-4DFC-448C-A7D4-C295AD5FD4E3}"/>
-    <hyperlink ref="A7" r:id="rId4" xr:uid="{8B093489-D272-45ED-9C6F-547E4D788C3F}"/>
-    <hyperlink ref="A8" r:id="rId5" xr:uid="{E2603058-DB8F-4835-838E-36657E9B6C0A}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{8A7740AB-CCA3-4932-AFC9-DB430BE99EE8}"/>
-    <hyperlink ref="A10" r:id="rId7" xr:uid="{20532DD6-F61B-4799-96C5-BC0218CDC291}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{F461F542-2D25-4E6E-94D0-8F7D6B1FDE6E}"/>
-    <hyperlink ref="A12" r:id="rId9" xr:uid="{044CB83D-F7D4-47F8-B3C7-7A55EB6430AD}"/>
-    <hyperlink ref="A14" r:id="rId10" xr:uid="{E02C74B2-0A5B-4228-8BFC-49E858730237}"/>
-    <hyperlink ref="A15" r:id="rId11" xr:uid="{97F222A2-E155-48FA-B6D9-682803AE862C}"/>
-    <hyperlink ref="A16" r:id="rId12" xr:uid="{6270B46B-282E-45B1-B9E8-F4EEE3C99F16}"/>
-    <hyperlink ref="A17" r:id="rId13" xr:uid="{CC92551D-77EF-4708-A5DF-182695A842DA}"/>
-    <hyperlink ref="A18" r:id="rId14" xr:uid="{F3406FA9-92AC-4649-91CB-BDACB273167C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2FB9D2DC-88F9-4B2D-8B07-2AD0A5941689}">
+          <x14:formula1>
+            <xm:f>data!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FA41776-A8B2-41D4-962D-58E40DD6F8EB}">
           <x14:formula1>
             <xm:f>data!$A$2:$A$5</xm:f>
@@ -934,18 +537,6 @@
           </x14:formula1>
           <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2FB9D2DC-88F9-4B2D-8B07-2AD0A5941689}">
-          <x14:formula1>
-            <xm:f>data!$C$2:$C$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{93037644-9E5B-4E5D-8296-16A9416E0151}">
-          <x14:formula1>
-            <xm:f>data!$C$2:$C$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -954,12 +545,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43AA28A4-1708-49C1-9939-94064891E6E1}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -968,7 +559,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -976,13 +567,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -998,13 +589,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1020,13 +611,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1042,10 +633,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1061,7 +655,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1077,7 +674,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1089,6 +689,26 @@
       <c r="I7" t="str">
         <f t="shared" si="1"/>
         <v>(4,'ScrumMaster'),</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/vendor_upload_template.xlsx
+++ b/public/templates/vendor_upload_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F039B800-EE24-4F3A-86A2-ADBC6810A419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B0DB938-8532-4744-B2FE-2E5516201F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor" sheetId="1" r:id="rId1"/>
-    <sheet name="data" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="data" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Email</t>
   </si>
@@ -72,30 +72,18 @@
     <t>SubTeams</t>
   </si>
   <si>
-    <t>BA</t>
-  </si>
-  <si>
     <t>QA</t>
   </si>
   <si>
     <t>DEV</t>
   </si>
   <si>
-    <t>DBA</t>
-  </si>
-  <si>
-    <t>PMO</t>
-  </si>
-  <si>
     <t>Optime-Tech</t>
   </si>
   <si>
     <t>Yovant</t>
   </si>
   <si>
-    <t>ScrumMaster</t>
-  </si>
-  <si>
     <t>LTM</t>
   </si>
   <si>
@@ -108,13 +96,61 @@
     <t>EY</t>
   </si>
   <si>
-    <t>DuckCreek</t>
-  </si>
-  <si>
     <t>NTT Data</t>
   </si>
   <si>
     <t>Invenger</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>DTC</t>
+  </si>
+  <si>
+    <t>MySlide</t>
+  </si>
+  <si>
+    <t>Websites</t>
+  </si>
+  <si>
+    <t>Integrations</t>
+  </si>
+  <si>
+    <t>PolicyAttach</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>IT GRC</t>
+  </si>
+  <si>
+    <t>IT Ops</t>
+  </si>
+  <si>
+    <t>Delivery/Scrum Master</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>Release Management</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>EITACIES</t>
+  </si>
+  <si>
+    <t>Exavalu</t>
+  </si>
+  <si>
+    <t>NEST</t>
   </si>
 </sst>
 </file>
@@ -521,21 +557,21 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2FB9D2DC-88F9-4B2D-8B07-2AD0A5941689}">
           <x14:formula1>
-            <xm:f>data!$C$2:$C$14</xm:f>
+            <xm:f>data!$C$2:$C$20</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FA41776-A8B2-41D4-962D-58E40DD6F8EB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A337F88A-649D-4D4A-B1A4-B345B60A9A35}">
           <x14:formula1>
-            <xm:f>data!$A$2:$A$5</xm:f>
+            <xm:f>data!$B$2:$B$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E4E6CD72-44CA-4FF2-8BE5-60B327E81574}">
+          <x14:formula1>
+            <xm:f>data!$A$2:$A$24</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A337F88A-649D-4D4A-B1A4-B345B60A9A35}">
-          <x14:formula1>
-            <xm:f>data!$B$2:$B$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -545,16 +581,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43AA28A4-1708-49C1-9939-94064891E6E1}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -565,150 +600,126 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2" t="str">
-        <f>"'"&amp;B2&amp;"'),"</f>
-        <v>'PMO'),</v>
-      </c>
-      <c r="I2" t="str">
-        <f>"("&amp;G2&amp;","&amp;H2</f>
-        <v>(4,'PMO'),</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H7" si="0">"'"&amp;B3&amp;"'),"</f>
-        <v>'DEV'),</v>
-      </c>
-      <c r="I3" t="str">
-        <f t="shared" ref="I3:I7" si="1">"("&amp;G3&amp;","&amp;H3</f>
-        <v>(4,'DEV'),</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>'QA'),</v>
-      </c>
-      <c r="I4" t="str">
-        <f t="shared" si="1"/>
-        <v>(4,'QA'),</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>'BA'),</v>
-      </c>
-      <c r="I5" t="str">
-        <f t="shared" si="1"/>
-        <v>(4,'BA'),</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>'DBA'),</v>
-      </c>
-      <c r="I6" t="str">
-        <f t="shared" si="1"/>
-        <v>(4,'DBA'),</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>'ScrumMaster'),</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="1"/>
-        <v>(4,'ScrumMaster'),</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
-        <v>25</v>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/vendor_upload_template.xlsx
+++ b/public/templates/vendor_upload_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B0DB938-8532-4744-B2FE-2E5516201F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEB93E9-C115-47E8-A0B4-0BEB78A90A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
   </bookViews>
@@ -166,12 +166,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -186,8 +192,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,13 +597,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
